--- a/excel/read_cauhoi.xlsx
+++ b/excel/read_cauhoi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL\my-project\QuanLyQuiz\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DF6E7AD-ED50-4656-8C4B-2A4D3D3F19E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE7B403-6203-4497-8550-221AD80AE254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{711CA27E-4026-42C8-89EF-3B26A3217562}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>Nội dung</t>
   </si>
@@ -50,12 +50,6 @@
     <t>Môn</t>
   </si>
   <si>
-    <t>Từ khoá nào được dùng để khai báo một hằng số trong Java?</t>
-  </si>
-  <si>
-    <t>Trong Java, một lớp có thể kế thừa trực tiếp từ nhiều lớp cha khác nhau</t>
-  </si>
-  <si>
     <t>Dễ</t>
   </si>
   <si>
@@ -68,7 +62,67 @@
     <t>Đúng Sai</t>
   </si>
   <si>
-    <t>Lập trình Java</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Khó</t>
+  </si>
+  <si>
+    <t>Đúng sai</t>
+  </si>
+  <si>
+    <t>Spring Boot hỗ trợ đóng gói ứng dụng thành file .jar để chạy độc lập.</t>
+  </si>
+  <si>
+    <t>@RestController là sự kết hợp giữa @Controller và @Service</t>
+  </si>
+  <si>
+    <t>Để thay đổi cổng (port) mặc định, ta dùng thuộc tính server.____ trong file properties.</t>
+  </si>
+  <si>
+    <t>Annotation dùng để đánh dấu một class là tầng truy cập dữ liệu (Data Access) là @____.</t>
+  </si>
+  <si>
+    <t>Scope mặc định của một Bean trong Spring Framework là gì?</t>
+  </si>
+  <si>
+    <t>Điền khuyết</t>
+  </si>
+  <si>
+    <t>Java Spring Boot</t>
+  </si>
+  <si>
+    <t>Đúng</t>
+  </si>
+  <si>
+    <t>Sai</t>
+  </si>
+  <si>
+    <t>Prototype</t>
+  </si>
+  <si>
+    <t>Request</t>
+  </si>
+  <si>
+    <t>Singleton</t>
+  </si>
+  <si>
+    <t>Session</t>
+  </si>
+  <si>
+    <t>port</t>
+  </si>
+  <si>
+    <t>Repository</t>
   </si>
 </sst>
 </file>
@@ -449,16 +503,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CC97097-FCAC-411D-8C2A-A14FA310DA94}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="62.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="77.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" customWidth="1"/>
     <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" customWidth="1"/>
+    <col min="8" max="8" width="9.36328125" customWidth="1"/>
+    <col min="9" max="9" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,32 +530,116 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
         <v>10</v>
       </c>
     </row>
